--- a/12610223.xlsx
+++ b/12610223.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Desktop\776\CAP776-GROUP-I-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A80D3C-DB5C-4F95-8D8C-599BF51172E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1810CF50-A04C-4926-80BF-C39810E8DBE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3428,29 +3428,51 @@
         <v>64</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A71" s="8">
         <v>46316</v>
       </c>
-      <c r="B71" s="9"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="9"/>
-      <c r="E71" s="9"/>
-      <c r="F71" s="9"/>
-      <c r="G71" s="9"/>
-      <c r="H71" s="9"/>
-      <c r="I71" s="10" t="str">
+      <c r="B71" s="9">
+        <v>300</v>
+      </c>
+      <c r="C71" s="9">
+        <v>40</v>
+      </c>
+      <c r="D71" s="9">
+        <v>240</v>
+      </c>
+      <c r="E71" s="9">
+        <v>60</v>
+      </c>
+      <c r="F71" s="9">
+        <v>350</v>
+      </c>
+      <c r="G71" s="9">
+        <v>7</v>
+      </c>
+      <c r="H71" s="9">
+        <v>120</v>
+      </c>
+      <c r="I71" s="10">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J71" s="10" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J71" s="10">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K71" s="11"/>
-      <c r="L71" s="11"/>
-      <c r="M71" s="11"/>
-      <c r="N71" s="12"/>
+        <v>330</v>
+      </c>
+      <c r="K71" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L71" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M71" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N71" s="12" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="8"/>

--- a/12610223.xlsx
+++ b/12610223.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Desktop\776\CAP776-GROUP-I-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1810CF50-A04C-4926-80BF-C39810E8DBE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C03FBC-F925-404B-BEDE-0BA1C863CD13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -297,6 +297,12 @@
   <si>
     <t>clearing concepts of python.</t>
   </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>working with python functions.</t>
+  </si>
 </sst>
 </file>
 
@@ -400,7 +406,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -423,11 +429,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -452,6 +469,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -924,7 +944,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N395"/>
+  <dimension ref="A1:O395"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
@@ -941,74 +961,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="16">
         <v>12610223</v>
       </c>
-      <c r="G2" s="15"/>
+      <c r="G2" s="16"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="G3" s="15"/>
+      <c r="G3" s="16"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -3262,7 +3282,7 @@
       <c r="M64" s="11"/>
       <c r="N64" s="12"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" s="8">
         <v>46310</v>
       </c>
@@ -3286,7 +3306,7 @@
       <c r="M65" s="11"/>
       <c r="N65" s="12"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" s="8">
         <v>46311</v>
       </c>
@@ -3310,7 +3330,7 @@
       <c r="M66" s="11"/>
       <c r="N66" s="12"/>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" s="8">
         <v>46312</v>
       </c>
@@ -3334,7 +3354,7 @@
       <c r="M67" s="11"/>
       <c r="N67" s="12"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" s="8">
         <v>46313</v>
       </c>
@@ -3358,7 +3378,7 @@
       <c r="M68" s="11"/>
       <c r="N68" s="12"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" s="8">
         <v>46314</v>
       </c>
@@ -3382,7 +3402,7 @@
       <c r="M69" s="11"/>
       <c r="N69" s="12"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" s="8">
         <v>46315</v>
       </c>
@@ -3428,7 +3448,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="71" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A71" s="8">
         <v>46316</v>
       </c>
@@ -3445,21 +3465,21 @@
         <v>60</v>
       </c>
       <c r="F71" s="9">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="G71" s="9">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H71" s="9">
         <v>120</v>
       </c>
       <c r="I71" s="10">
         <f t="shared" si="4"/>
-        <v>1110</v>
+        <v>960</v>
       </c>
       <c r="J71" s="10">
         <f t="shared" si="5"/>
-        <v>330</v>
+        <v>480</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>49</v>
@@ -3473,52 +3493,103 @@
       <c r="N71" s="12" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="8"/>
-      <c r="B72" s="9"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="9"/>
-      <c r="E72" s="9"/>
-      <c r="F72" s="9"/>
-      <c r="G72" s="9"/>
-      <c r="H72" s="9"/>
-      <c r="I72" s="10" t="str">
+      <c r="O71" s="13" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A72" s="8">
+        <v>46317</v>
+      </c>
+      <c r="B72" s="9">
+        <v>300</v>
+      </c>
+      <c r="C72" s="9">
+        <v>40</v>
+      </c>
+      <c r="D72" s="9">
+        <v>160</v>
+      </c>
+      <c r="E72" s="9">
+        <v>60</v>
+      </c>
+      <c r="F72" s="9">
+        <v>350</v>
+      </c>
+      <c r="G72" s="9">
+        <v>7</v>
+      </c>
+      <c r="H72" s="9">
+        <v>120</v>
+      </c>
+      <c r="I72" s="10">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J72" s="10" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J72" s="10">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K72" s="11"/>
-      <c r="L72" s="11"/>
-      <c r="M72" s="11"/>
-      <c r="N72" s="12"/>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="8"/>
-      <c r="B73" s="9"/>
-      <c r="C73" s="9"/>
-      <c r="D73" s="9"/>
-      <c r="E73" s="9"/>
-      <c r="F73" s="9"/>
-      <c r="G73" s="9"/>
-      <c r="H73" s="9"/>
-      <c r="I73" s="10" t="str">
+        <v>410</v>
+      </c>
+      <c r="K72" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L72" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M72" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N72" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A73" s="8">
+        <v>46318</v>
+      </c>
+      <c r="B73" s="9">
+        <v>300</v>
+      </c>
+      <c r="C73" s="9">
+        <v>50</v>
+      </c>
+      <c r="D73" s="9">
+        <v>180</v>
+      </c>
+      <c r="E73" s="9">
+        <v>90</v>
+      </c>
+      <c r="F73" s="9">
+        <v>350</v>
+      </c>
+      <c r="G73" s="9">
+        <v>7</v>
+      </c>
+      <c r="H73" s="9">
+        <v>120</v>
+      </c>
+      <c r="I73" s="10">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J73" s="10" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J73" s="10">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K73" s="11"/>
-      <c r="L73" s="11"/>
-      <c r="M73" s="11"/>
-      <c r="N73" s="12"/>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+        <v>350</v>
+      </c>
+      <c r="K73" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L73" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M73" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N73" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" s="8"/>
       <c r="B74" s="9"/>
       <c r="C74" s="9"/>
@@ -3540,7 +3611,7 @@
       <c r="M74" s="11"/>
       <c r="N74" s="12"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" s="8"/>
       <c r="B75" s="9"/>
       <c r="C75" s="9"/>
@@ -3562,7 +3633,7 @@
       <c r="M75" s="11"/>
       <c r="N75" s="12"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" s="8"/>
       <c r="B76" s="9"/>
       <c r="C76" s="9"/>
@@ -3584,7 +3655,7 @@
       <c r="M76" s="11"/>
       <c r="N76" s="12"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" s="8"/>
       <c r="B77" s="9"/>
       <c r="C77" s="9"/>
@@ -3606,7 +3677,7 @@
       <c r="M77" s="11"/>
       <c r="N77" s="12"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" s="8"/>
       <c r="B78" s="9"/>
       <c r="C78" s="9"/>
@@ -3628,7 +3699,7 @@
       <c r="M78" s="11"/>
       <c r="N78" s="12"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" s="8"/>
       <c r="B79" s="9"/>
       <c r="C79" s="9"/>
@@ -3650,7 +3721,7 @@
       <c r="M79" s="11"/>
       <c r="N79" s="12"/>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" s="8"/>
       <c r="B80" s="9"/>
       <c r="C80" s="9"/>

--- a/12610223.xlsx
+++ b/12610223.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Desktop\776\CAP776-GROUP-I-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C03FBC-F925-404B-BEDE-0BA1C863CD13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{079E00B7-ED24-4465-BB8F-BE4A55E0F41C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -302,6 +302,9 @@
   </si>
   <si>
     <t>working with python functions.</t>
+  </si>
+  <si>
+    <t>working with python built in functions.</t>
   </si>
 </sst>
 </file>
@@ -3589,27 +3592,51 @@
         <v>91</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A74" s="8"/>
-      <c r="B74" s="9"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="9"/>
-      <c r="F74" s="9"/>
-      <c r="G74" s="9"/>
-      <c r="H74" s="9"/>
-      <c r="I74" s="10" t="str">
+    <row r="74" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A74" s="8">
+        <v>46319</v>
+      </c>
+      <c r="B74" s="9">
+        <v>360</v>
+      </c>
+      <c r="C74" s="9">
+        <v>50</v>
+      </c>
+      <c r="D74" s="9">
+        <v>240</v>
+      </c>
+      <c r="E74" s="9">
+        <v>60</v>
+      </c>
+      <c r="F74" s="9">
+        <v>0</v>
+      </c>
+      <c r="G74" s="9">
+        <v>0</v>
+      </c>
+      <c r="H74" s="9">
+        <v>120</v>
+      </c>
+      <c r="I74" s="10">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J74" s="10" t="str">
+        <v>830</v>
+      </c>
+      <c r="J74" s="10">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K74" s="11"/>
-      <c r="L74" s="11"/>
-      <c r="M74" s="11"/>
-      <c r="N74" s="12"/>
+        <v>610</v>
+      </c>
+      <c r="K74" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L74" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M74" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N74" s="12" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" s="8"/>

--- a/12610223.xlsx
+++ b/12610223.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Desktop\776\CAP776-GROUP-I-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{079E00B7-ED24-4465-BB8F-BE4A55E0F41C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54873874-D98F-43FE-A121-C7398210E43E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="94">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -305,6 +305,9 @@
   </si>
   <si>
     <t>working with python built in functions.</t>
+  </si>
+  <si>
+    <t>working with numpy,panndas.</t>
   </si>
 </sst>
 </file>
@@ -3639,26 +3642,50 @@
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A75" s="8"/>
-      <c r="B75" s="9"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9"/>
-      <c r="E75" s="9"/>
-      <c r="F75" s="9"/>
-      <c r="G75" s="9"/>
-      <c r="H75" s="9"/>
-      <c r="I75" s="10" t="str">
+      <c r="A75" s="8">
+        <v>46320</v>
+      </c>
+      <c r="B75" s="9">
+        <v>360</v>
+      </c>
+      <c r="C75" s="9">
+        <v>20</v>
+      </c>
+      <c r="D75" s="9">
+        <v>240</v>
+      </c>
+      <c r="E75" s="9">
+        <v>240</v>
+      </c>
+      <c r="F75" s="9">
+        <v>0</v>
+      </c>
+      <c r="G75" s="9">
+        <v>0</v>
+      </c>
+      <c r="H75" s="9">
+        <v>240</v>
+      </c>
+      <c r="I75" s="10">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J75" s="10" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J75" s="10">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K75" s="11"/>
-      <c r="L75" s="11"/>
-      <c r="M75" s="11"/>
-      <c r="N75" s="12"/>
+        <v>340</v>
+      </c>
+      <c r="K75" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L75" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M75" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N75" s="12" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" s="8"/>

--- a/12610223.xlsx
+++ b/12610223.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Desktop\776\CAP776-GROUP-I-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54873874-D98F-43FE-A121-C7398210E43E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F77B12-222D-4AD4-994E-911939450248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="95">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -308,6 +308,9 @@
   </si>
   <si>
     <t>working with numpy,panndas.</t>
+  </si>
+  <si>
+    <t>working with python slicing.</t>
   </si>
 </sst>
 </file>
@@ -3688,26 +3691,50 @@
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A76" s="8"/>
-      <c r="B76" s="9"/>
-      <c r="C76" s="9"/>
-      <c r="D76" s="9"/>
-      <c r="E76" s="9"/>
-      <c r="F76" s="9"/>
-      <c r="G76" s="9"/>
-      <c r="H76" s="9"/>
-      <c r="I76" s="10" t="str">
+      <c r="A76" s="8">
+        <v>46321</v>
+      </c>
+      <c r="B76" s="9">
+        <v>360</v>
+      </c>
+      <c r="C76" s="9">
+        <v>20</v>
+      </c>
+      <c r="D76" s="9">
+        <v>240</v>
+      </c>
+      <c r="E76" s="9">
+        <v>240</v>
+      </c>
+      <c r="F76" s="9">
+        <v>0</v>
+      </c>
+      <c r="G76" s="9">
+        <v>0</v>
+      </c>
+      <c r="H76" s="9">
+        <v>300</v>
+      </c>
+      <c r="I76" s="10">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J76" s="10" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J76" s="10">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K76" s="11"/>
-      <c r="L76" s="11"/>
-      <c r="M76" s="11"/>
-      <c r="N76" s="12"/>
+        <v>280</v>
+      </c>
+      <c r="K76" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L76" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M76" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N76" s="12" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" s="8"/>

--- a/12610223.xlsx
+++ b/12610223.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Desktop\776\CAP776-GROUP-I-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F77B12-222D-4AD4-994E-911939450248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F2AB415-314F-4295-8DC5-5500DE89BC3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -311,6 +311,9 @@
   </si>
   <si>
     <t>working with python slicing.</t>
+  </si>
+  <si>
+    <t>working with numpy libraries</t>
   </si>
 </sst>
 </file>
@@ -3737,26 +3740,50 @@
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A77" s="8"/>
-      <c r="B77" s="9"/>
-      <c r="C77" s="9"/>
-      <c r="D77" s="9"/>
-      <c r="E77" s="9"/>
-      <c r="F77" s="9"/>
-      <c r="G77" s="9"/>
-      <c r="H77" s="9"/>
-      <c r="I77" s="10" t="str">
+      <c r="A77" s="8">
+        <v>46322</v>
+      </c>
+      <c r="B77" s="9">
+        <v>360</v>
+      </c>
+      <c r="C77" s="9">
+        <v>40</v>
+      </c>
+      <c r="D77" s="9">
+        <v>180</v>
+      </c>
+      <c r="E77" s="9">
+        <v>240</v>
+      </c>
+      <c r="F77" s="9">
+        <v>400</v>
+      </c>
+      <c r="G77" s="9">
+        <v>8</v>
+      </c>
+      <c r="H77" s="9">
+        <v>220</v>
+      </c>
+      <c r="I77" s="10">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J77" s="10" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J77" s="10">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K77" s="11"/>
-      <c r="L77" s="11"/>
-      <c r="M77" s="11"/>
-      <c r="N77" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="K77" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L77" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M77" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N77" s="12" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" s="8"/>

--- a/12610223.xlsx
+++ b/12610223.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Desktop\776\CAP776-GROUP-I-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F2AB415-314F-4295-8DC5-5500DE89BC3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5926252-2CC2-4890-83CB-D3372EFAA22A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -314,6 +314,9 @@
   </si>
   <si>
     <t>working with numpy libraries</t>
+  </si>
+  <si>
+    <t>working with python numpy lib.</t>
   </si>
 </sst>
 </file>
@@ -3786,48 +3789,96 @@
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A78" s="8"/>
-      <c r="B78" s="9"/>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9"/>
-      <c r="G78" s="9"/>
-      <c r="H78" s="9"/>
-      <c r="I78" s="10" t="str">
+      <c r="A78" s="8">
+        <v>46323</v>
+      </c>
+      <c r="B78" s="9">
+        <v>360</v>
+      </c>
+      <c r="C78" s="9">
+        <v>30</v>
+      </c>
+      <c r="D78" s="9">
+        <v>180</v>
+      </c>
+      <c r="E78" s="9">
+        <v>120</v>
+      </c>
+      <c r="F78" s="9">
+        <v>200</v>
+      </c>
+      <c r="G78" s="9">
+        <v>4</v>
+      </c>
+      <c r="H78" s="9">
+        <v>180</v>
+      </c>
+      <c r="I78" s="10">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J78" s="10" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J78" s="10">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K78" s="11"/>
-      <c r="L78" s="11"/>
-      <c r="M78" s="11"/>
-      <c r="N78" s="12"/>
+        <v>370</v>
+      </c>
+      <c r="K78" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L78" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M78" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N78" s="12" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A79" s="8"/>
-      <c r="B79" s="9"/>
-      <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9"/>
-      <c r="G79" s="9"/>
-      <c r="H79" s="9"/>
-      <c r="I79" s="10" t="str">
+      <c r="A79" s="8">
+        <v>46324</v>
+      </c>
+      <c r="B79" s="9">
+        <v>360</v>
+      </c>
+      <c r="C79" s="9">
+        <v>30</v>
+      </c>
+      <c r="D79" s="9">
+        <v>300</v>
+      </c>
+      <c r="E79" s="9">
+        <v>120</v>
+      </c>
+      <c r="F79" s="9">
+        <v>350</v>
+      </c>
+      <c r="G79" s="9">
+        <v>7</v>
+      </c>
+      <c r="H79" s="9">
+        <v>180</v>
+      </c>
+      <c r="I79" s="10">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J79" s="10" t="str">
+        <v>1340</v>
+      </c>
+      <c r="J79" s="10">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K79" s="11"/>
-      <c r="L79" s="11"/>
-      <c r="M79" s="11"/>
-      <c r="N79" s="12"/>
+        <v>100</v>
+      </c>
+      <c r="K79" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="L79" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M79" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N79" s="12" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" s="8"/>
